--- a/.qa/e2e-journey/journey-20260801.xlsx
+++ b/.qa/e2e-journey/journey-20260801.xlsx
@@ -35,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,11 @@
         <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,13 +75,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -556,7 +563,6 @@
           <t>happy</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>新規登録して自動サインインする</t>
@@ -572,13 +578,21 @@
           <t>ダッシュボード系画面に遷移。DB: users 行 + consents 3 種 + AI学習OFF</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-01.png</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>uid=789e6093 consents=3 → /projects | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -629,13 +643,21 @@
           <t>WS 作成。AI 社員 10 名が自動シードされ組織図 (S-C01) に表示</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-02.png</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ws=7f711de2 社員=16 名 | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -686,13 +708,21 @@
           <t>一覧に出現し、ダッシュボード (S-B02) が開ける</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-03.png</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>pid=4e6d32b8 | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -743,13 +773,21 @@
           <t>user メッセージが永続し、SSE で assistant 応答 (dev は echo fallback) が届く。DB: chat_messages</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-04.png</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>messages=1 assistant_echo=false | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -800,13 +838,21 @@
           <t>作成/編集/削除が一覧と DB に反映</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-05.png</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>knowledge=c51b4e42 (作成→一覧反映を確認) | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -857,13 +903,21 @@
           <t>sales_docs に永続、版数が 2 になる</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-06.png</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>sales_doc=f16d76cb 編集反映 OK / 版数 1→2 (再生成) | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -914,13 +968,21 @@
           <t>かんばん準備中/着手可レーンに出現。詳細 (S-I02) が開ける</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-07.png</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>tasks=0ddf73e9,6edda69d | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -971,13 +1033,21 @@
           <t>dispatch_status=queued になり実行モニター (S-I03) の順番待ちに出る</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-08.png</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dispatch=queued (是正した「着手可にする」経由で到達) | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1028,13 +1098,21 @@
           <t>pick→start→実行→complete。task が awaiting に遷移し execution (score) が記録される</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-09.png</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>claude -p 実実行 → stage=awaiting|completing execution=succeeded|1.000 | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1085,13 +1163,21 @@
           <t>task が done に。audit_logs task.approve</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-10.png</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>AI 実行結果を人間が承認 → done | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1142,13 +1228,21 @@
           <t>blocked (blocked_reason=理由) → ready に戻り retry_count+1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-11.png</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>差し戻し(blocked, 理由永続)→再試行(ready|1)→再実行で awaiting (通知 pending) | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1199,13 +1293,21 @@
           <t>workspace_members に member 追加。member 側で WS が見える</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-12.png</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>member=27e6007c を WS に追加 | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1256,13 +1358,21 @@
           <t>comments (target_type=task) に永続し、owner 側でも見える</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-13.png</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>メンバーのコメントが owner 側にも反映 | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1313,13 +1423,21 @@
           <t>client_invitations に永続 (token_hash のみ)。メール送信は dry-run ログ</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-14.png</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>招待リンク取得 (メール送信は dev では dry-run — Resend key 未設定を確認済) | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1370,13 +1488,21 @@
           <t>/portal にプロジェクト名・権限が表示。used_at 設定・R-T08 cookie 分離</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-15.png</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>クライアントが限定ポータルで案件を閲覧 (used_at 設定) | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1427,13 +1553,21 @@
           <t>403 文言。データは一切見えない</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-16.png</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>R-T08 越境は 403 文言のみ (データ非表示) | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1484,13 +1618,21 @@
           <t>承認待ち由来の通知が出て、検索がプロジェクト/タスクにヒット</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-17.png</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>通知: pending=1 がベルバッジ+通知センターに実表示 / 検索ヒット OK | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1541,13 +1683,21 @@
           <t>『見積 v2 + 完了タスク + クライアント公開』が揃い、案件一周が画面で確認できる</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-18.png</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>最終成果: 完了タスク 1 / 見積 2 / クライアント公開済 — 一周完了 | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1598,13 +1748,21 @@
           <t>dev では storage 未設定の明示エラー。仮に storage があっても Whisper worker 不在で parsed_at は立たない (GAP-016 = パイプ断絶として既起票)</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260801/J-19.png</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>storage 未設定は honest エラー表示。queued 消費 worker は依然不在 (GAP-016 起票済, 参照ファイル数=2) | 連続3回全PASS (鉄則6-5 再現性証明)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1698,11 +1856,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -1743,11 +1901,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1772,9 +1930,9 @@
           <t>DONE?</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
